--- a/template.xlsx
+++ b/template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://intcap-my.sharepoint.com/personal/divo_pulitika_intercapital_hr/Documents/Desktop/Tradeweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{424C5619-5F12-4F62-870F-0BFE263568B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8908973-4302-465A-B495-A8D40F9DCABD}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{424C5619-5F12-4F62-870F-0BFE263568B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E334B66-657C-4148-BAB3-87D103CA2BE3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{696EB1AD-4F22-4798-B4E1-166961222168}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{696EB1AD-4F22-4798-B4E1-166961222168}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="77">
   <si>
     <t>FUND_LEVEL</t>
   </si>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>[TRADE_DATE]</t>
+  </si>
+  <si>
+    <t>[CLASS_CURRENCY]</t>
   </si>
 </sst>
 </file>
@@ -660,49 +663,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27200E13-B81A-40C0-9C71-E88C7ACC4906}">
   <dimension ref="A1:V44"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="20" style="1" customWidth="1"/>
-    <col min="7" max="7" width="34.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.33203125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.109375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="21.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="24.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.109375" style="1"/>
+    <col min="7" max="7" width="34.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -710,7 +713,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -719,7 +722,7 @@
       </c>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -727,7 +730,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -735,15 +738,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -755,7 +758,7 @@
       </c>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -767,7 +770,7 @@
       </c>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -778,27 +781,27 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -806,23 +809,23 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="2"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -830,7 +833,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -838,12 +841,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>22</v>
       </c>
@@ -911,7 +914,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>65</v>
       </c>
@@ -942,17 +945,17 @@
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="L27" s="5"/>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>43</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="2"/>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>22</v>
       </c>
@@ -1002,16 +1005,16 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K31" s="1"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>47</v>
       </c>
@@ -1034,34 +1037,34 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C35" s="6"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C36" s="6"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C37" s="6"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C38" s="6"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C39" s="6"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C40" s="6"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C41" s="6"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C42" s="6"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C43" s="6"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C44" s="6"/>
     </row>
   </sheetData>

--- a/template.xlsx
+++ b/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://intcap-my.sharepoint.com/personal/divo_pulitika_intercapital_hr/Documents/Desktop/Tradeweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{424C5619-5F12-4F62-870F-0BFE263568B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E334B66-657C-4148-BAB3-87D103CA2BE3}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{424C5619-5F12-4F62-870F-0BFE263568B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56B8A7B9-B20B-4A42-91BA-4DC4831BE866}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{696EB1AD-4F22-4798-B4E1-166961222168}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="43200" windowHeight="23445" xr2:uid="{696EB1AD-4F22-4798-B4E1-166961222168}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="76">
   <si>
     <t>FUND_LEVEL</t>
   </si>
@@ -264,9 +264,6 @@
   </si>
   <si>
     <t>[TRADE_DATE]</t>
-  </si>
-  <si>
-    <t>[CLASS_CURRENCY]</t>
   </si>
 </sst>
 </file>
@@ -743,7 +740,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
